--- a/Document/RTM/RTM_DemoWebShop_MB.xlsx
+++ b/Document/RTM/RTM_DemoWebShop_MB.xlsx
@@ -1,16 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69E71A0D-B216-493F-8A62-C6210066D10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9963c16bba70e78d/Documents/GitHub/AutomationWebShopDemo/Document/RTM/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="RTM" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -140,9 +144,6 @@
     <t>As a shopper, I want to manage my cart so I can review and adjust my order before checkout.</t>
   </si>
   <si>
-    <t>TC-Cart-01 to TC-Cart-03</t>
-  </si>
-  <si>
     <t>RQ-5</t>
   </si>
   <si>
@@ -155,17 +156,20 @@
     <t>As a logged-in user, I want to save products to my wishlist so I can purchase them later.</t>
   </si>
   <si>
-    <t>TC-WISH-01 to TC-WISH-03</t>
-  </si>
-  <si>
     <t>TC-WISH-03 Failed – Bug-Wish-02</t>
+  </si>
+  <si>
+    <t>TC-Cart-01 to TC-Cart-05</t>
+  </si>
+  <si>
+    <t>TC-WISH-01 to TC-WISH-04</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,10 +305,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,9 +610,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -620,33 +624,33 @@
     <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
-    <row r="2" spans="1:8" ht="21.95" customHeight="1">
+    <row r="2" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
       <c r="E2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
     </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1">
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -672,7 +676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="50.1" customHeight="1">
+    <row r="4" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -698,7 +702,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="50.1" customHeight="1">
+    <row r="5" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>19</v>
       </c>
@@ -724,7 +728,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="50.1" customHeight="1">
+    <row r="6" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -750,7 +754,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="50.1" customHeight="1">
+    <row r="7" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>30</v>
       </c>
@@ -767,7 +771,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>17</v>
@@ -776,30 +780,30 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="50.1" customHeight="1">
+    <row r="8" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
